--- a/output_data/charts/0500000US39101.xlsx
+++ b/output_data/charts/0500000US39101.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.4980514302050889</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.5456753308637041</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5520890683305806</c:v>
+                  <c:v>0.5520721822908702</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5711223396110856</c:v>
+                  <c:v>0.5709474973212919</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5757711773901468</c:v>
+                  <c:v>0.5729682854311199</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.5659126304914343</c:v>
+                  <c:v>0.5630283210958228</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5401994582615119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>5.677184429497886</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>6.300628679465698</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.384963601884137</c:v>
+                  <c:v>6.383239027374215</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.571734803246057</c:v>
+                  <c:v>6.580437777437624</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.314909687504837</c:v>
+                  <c:v>6.321233894945491</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.50414025998057</c:v>
+                  <c:v>6.509532917874992</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.557805959123368</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2.272077521479408</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>2.920515855326867</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.028078546522297</c:v>
+                  <c:v>3.024927358923383</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.085285561169806</c:v>
+                  <c:v>3.082810347466708</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.214722407094987</c:v>
+                  <c:v>3.227205153617443</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.338421921018951</c:v>
+                  <c:v>3.373542296538533</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.53976852991874</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1880858875396861</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.2582350861552177</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2645745396708876</c:v>
+                  <c:v>0.264566447469032</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2756086357372531</c:v>
+                  <c:v>0.2755242614419103</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.2755034128372208</c:v>
+                  <c:v>0.2725470763131814</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2929792909901158</c:v>
+                  <c:v>0.2899981489479854</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2970327505540507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.495658977715584</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.902946646786664</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.017189698415612</c:v>
+                  <c:v>2.015598715399908</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.128311131526566</c:v>
+                  <c:v>2.126128884126741</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.241173830271324</c:v>
+                  <c:v>2.23302775024777</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.300658432406594</c:v>
+                  <c:v>2.273708891219843</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.357793646885003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>89.86894175356235</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>88.07199840140186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87.75310454517648</c:v>
+                  <c:v>87.75959626854259</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>87.36793752870923</c:v>
+                  <c:v>87.36415123220573</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>87.37791948490148</c:v>
+                  <c:v>87.373017839445</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>86.99788746511233</c:v>
+                  <c:v>86.99018942432282</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>86.70739965525732</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.5520890683305806</v>
+        <v>0.5520721822908702</v>
       </c>
       <c r="C12" s="2">
-        <v>6.384963601884137</v>
+        <v>6.383239027374215</v>
       </c>
       <c r="D12" s="2">
-        <v>3.028078546522297</v>
+        <v>3.024927358923383</v>
       </c>
       <c r="E12" s="2">
-        <v>0.2645745396708876</v>
+        <v>0.264566447469032</v>
       </c>
       <c r="F12" s="2">
-        <v>2.017189698415612</v>
+        <v>2.015598715399908</v>
       </c>
       <c r="G12" s="2">
-        <v>87.75310454517648</v>
+        <v>87.75959626854259</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.5711223396110856</v>
+        <v>0.5709474973212919</v>
       </c>
       <c r="C13" s="2">
-        <v>6.571734803246057</v>
+        <v>6.580437777437624</v>
       </c>
       <c r="D13" s="2">
-        <v>3.085285561169806</v>
+        <v>3.082810347466708</v>
       </c>
       <c r="E13" s="2">
-        <v>0.2756086357372531</v>
+        <v>0.2755242614419103</v>
       </c>
       <c r="F13" s="2">
-        <v>2.128311131526566</v>
+        <v>2.126128884126741</v>
       </c>
       <c r="G13" s="2">
-        <v>87.36793752870923</v>
+        <v>87.36415123220573</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.5757711773901468</v>
+        <v>0.5729682854311199</v>
       </c>
       <c r="C14" s="2">
-        <v>6.314909687504837</v>
+        <v>6.321233894945491</v>
       </c>
       <c r="D14" s="2">
-        <v>3.214722407094987</v>
+        <v>3.227205153617443</v>
       </c>
       <c r="E14" s="2">
-        <v>0.2755034128372208</v>
+        <v>0.2725470763131814</v>
       </c>
       <c r="F14" s="2">
-        <v>2.241173830271324</v>
+        <v>2.23302775024777</v>
       </c>
       <c r="G14" s="2">
-        <v>87.37791948490148</v>
+        <v>87.373017839445</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.5659126304914343</v>
+        <v>0.5630283210958228</v>
       </c>
       <c r="C15" s="2">
-        <v>6.50414025998057</v>
+        <v>6.509532917874992</v>
       </c>
       <c r="D15" s="2">
-        <v>3.338421921018951</v>
+        <v>3.373542296538533</v>
       </c>
       <c r="E15" s="2">
-        <v>0.2929792909901158</v>
+        <v>0.2899981489479854</v>
       </c>
       <c r="F15" s="2">
-        <v>2.300658432406594</v>
+        <v>2.273708891219843</v>
       </c>
       <c r="G15" s="2">
-        <v>86.99788746511233</v>
+        <v>86.99018942432282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.5401994582615119</v>
+      </c>
+      <c r="C16" s="2">
+        <v>6.557805959123368</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3.53976852991874</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.2970327505540507</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2.357793646885003</v>
+      </c>
+      <c r="G16" s="2">
+        <v>86.70739965525732</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39101.xlsx
+++ b/output_data/charts/0500000US39101.xlsx
@@ -226,34 +226,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.4980514302050889</c:v>
+                  <c:v>0.4980589244334768</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5374245654066713</c:v>
+                  <c:v>0.5360440847460172</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5324203254852867</c:v>
+                  <c:v>0.5280866665660787</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5727619855748833</c:v>
+                  <c:v>0.5684919046752774</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5423718513566892</c:v>
+                  <c:v>0.5395874815704276</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.559034672369024</c:v>
+                  <c:v>0.5547829010713576</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5665765641941938</c:v>
+                  <c:v>0.569752699833504</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.5574923594366716</c:v>
+                  <c:v>0.5747126436781609</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5532968544615291</c:v>
+                  <c:v>0.5792715545569872</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5456753308637041</c:v>
+                  <c:v>0.5760988124683145</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.5520721822908702</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>5.677184429497886</c:v>
+                  <c:v>5.677269854645039</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.875641756988021</c:v>
+                  <c:v>5.869457499361852</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.051190781436178</c:v>
+                  <c:v>6.044329103610604</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.07158009576338</c:v>
+                  <c:v>6.056333757807289</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.195496946309745</c:v>
+                  <c:v>6.180176619902418</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.277684435619367</c:v>
+                  <c:v>6.253916339349849</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.420182953833936</c:v>
+                  <c:v>6.389478668642217</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.368927863867431</c:v>
+                  <c:v>6.349499047267811</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.329288050622077</c:v>
+                  <c:v>6.304736576642671</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.300628679465698</c:v>
+                  <c:v>6.257201235155854</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>6.383239027374215</c:v>
@@ -488,34 +488,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>2.272077521479408</c:v>
+                  <c:v>2.270606999909718</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.265289578767226</c:v>
+                  <c:v>2.259793690595955</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.340839504683188</c:v>
+                  <c:v>2.335651885269399</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.310746105824596</c:v>
+                  <c:v>2.301255230125523</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.467260186563763</c:v>
+                  <c:v>2.459302944171695</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.552314036963495</c:v>
+                  <c:v>2.544665372682673</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.596172935660726</c:v>
+                  <c:v>2.582980738387279</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.659991092408582</c:v>
+                  <c:v>2.618476857827771</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.853605600220096</c:v>
+                  <c:v>2.789368303605545</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.920515855326867</c:v>
+                  <c:v>2.846696265343431</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>3.024927358923383</c:v>
@@ -619,34 +619,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.1880858875396861</c:v>
+                  <c:v>0.1880887176863583</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1951541717957186</c:v>
+                  <c:v>0.1951981260979894</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2021085654816669</c:v>
+                  <c:v>0.2036905713897732</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2121340687314383</c:v>
+                  <c:v>0.2122369777454369</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.2096563459025858</c:v>
+                  <c:v>0.2112750984177167</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2153658164044601</c:v>
+                  <c:v>0.2170225122648286</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2183839587055787</c:v>
+                  <c:v>0.2214856339835337</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.2365119100640425</c:v>
+                  <c:v>0.2397197123363452</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2567786506893284</c:v>
+                  <c:v>0.2583031470188149</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2582350861552177</c:v>
+                  <c:v>0.264237321985467</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.264566447469032</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.495658977715584</c:v>
+                  <c:v>1.495681483041921</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.523703725943495</c:v>
+                  <c:v>1.525548431658133</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.458499871796805</c:v>
+                  <c:v>1.465063294959036</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.533426268258682</c:v>
+                  <c:v>1.546297980716755</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.618000060769955</c:v>
+                  <c:v>1.635482056816282</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.707652359859478</c:v>
+                  <c:v>1.730066787913986</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.777614880652403</c:v>
+                  <c:v>1.802434814486688</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.804555157956169</c:v>
+                  <c:v>1.828631138975966</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.857059884449607</c:v>
+                  <c:v>1.881486236569</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.902946646786664</c:v>
+                  <c:v>1.921865638394298</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>2.015598715399908</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>89.86894175356235</c:v>
+                  <c:v>89.8702940202835</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>89.60278620109887</c:v>
+                  <c:v>89.61395816754005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>89.41494095111688</c:v>
+                  <c:v>89.42317847820512</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>89.29935147584702</c:v>
+                  <c:v>89.31538414892972</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>88.96721460909727</c:v>
+                  <c:v>88.97417579912145</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>88.68794867878418</c:v>
+                  <c:v>88.69954608671731</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>88.42106870695316</c:v>
+                  <c:v>88.43386744466677</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>88.37252161626711</c:v>
+                  <c:v>88.38896059991394</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>88.14997095955736</c:v>
+                  <c:v>88.18683418160698</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>88.07199840140186</c:v>
+                  <c:v>88.13390072665264</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>87.75959626854259</c:v>
@@ -1396,22 +1396,22 @@
         <v>2010</v>
       </c>
       <c r="B2" s="2">
-        <v>0.4980514302050889</v>
+        <v>0.4980589244334768</v>
       </c>
       <c r="C2" s="2">
-        <v>5.677184429497886</v>
+        <v>5.677269854645039</v>
       </c>
       <c r="D2" s="2">
-        <v>2.272077521479408</v>
+        <v>2.270606999909718</v>
       </c>
       <c r="E2" s="2">
-        <v>0.1880858875396861</v>
+        <v>0.1880887176863583</v>
       </c>
       <c r="F2" s="2">
-        <v>1.495658977715584</v>
+        <v>1.495681483041921</v>
       </c>
       <c r="G2" s="2">
-        <v>89.86894175356235</v>
+        <v>89.8702940202835</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5374245654066713</v>
+        <v>0.5360440847460172</v>
       </c>
       <c r="C3" s="2">
-        <v>5.875641756988021</v>
+        <v>5.869457499361852</v>
       </c>
       <c r="D3" s="2">
-        <v>2.265289578767226</v>
+        <v>2.259793690595955</v>
       </c>
       <c r="E3" s="2">
-        <v>0.1951541717957186</v>
+        <v>0.1951981260979894</v>
       </c>
       <c r="F3" s="2">
-        <v>1.523703725943495</v>
+        <v>1.525548431658133</v>
       </c>
       <c r="G3" s="2">
-        <v>89.60278620109887</v>
+        <v>89.61395816754005</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5324203254852867</v>
+        <v>0.5280866665660787</v>
       </c>
       <c r="C4" s="2">
-        <v>6.051190781436178</v>
+        <v>6.044329103610604</v>
       </c>
       <c r="D4" s="2">
-        <v>2.340839504683188</v>
+        <v>2.335651885269399</v>
       </c>
       <c r="E4" s="2">
-        <v>0.2021085654816669</v>
+        <v>0.2036905713897732</v>
       </c>
       <c r="F4" s="2">
-        <v>1.458499871796805</v>
+        <v>1.465063294959036</v>
       </c>
       <c r="G4" s="2">
-        <v>89.41494095111688</v>
+        <v>89.42317847820512</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1465,22 +1465,22 @@
         <v>2013</v>
       </c>
       <c r="B5" s="2">
-        <v>0.5727619855748833</v>
+        <v>0.5684919046752774</v>
       </c>
       <c r="C5" s="2">
-        <v>6.07158009576338</v>
+        <v>6.056333757807289</v>
       </c>
       <c r="D5" s="2">
-        <v>2.310746105824596</v>
+        <v>2.301255230125523</v>
       </c>
       <c r="E5" s="2">
-        <v>0.2121340687314383</v>
+        <v>0.2122369777454369</v>
       </c>
       <c r="F5" s="2">
-        <v>1.533426268258682</v>
+        <v>1.546297980716755</v>
       </c>
       <c r="G5" s="2">
-        <v>89.29935147584702</v>
+        <v>89.31538414892972</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1488,22 +1488,22 @@
         <v>2014</v>
       </c>
       <c r="B6" s="2">
-        <v>0.5423718513566892</v>
+        <v>0.5395874815704276</v>
       </c>
       <c r="C6" s="2">
-        <v>6.195496946309745</v>
+        <v>6.180176619902418</v>
       </c>
       <c r="D6" s="2">
-        <v>2.467260186563763</v>
+        <v>2.459302944171695</v>
       </c>
       <c r="E6" s="2">
-        <v>0.2096563459025858</v>
+        <v>0.2112750984177167</v>
       </c>
       <c r="F6" s="2">
-        <v>1.618000060769955</v>
+        <v>1.635482056816282</v>
       </c>
       <c r="G6" s="2">
-        <v>88.96721460909727</v>
+        <v>88.97417579912145</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.559034672369024</v>
+        <v>0.5547829010713576</v>
       </c>
       <c r="C7" s="2">
-        <v>6.277684435619367</v>
+        <v>6.253916339349849</v>
       </c>
       <c r="D7" s="2">
-        <v>2.552314036963495</v>
+        <v>2.544665372682673</v>
       </c>
       <c r="E7" s="2">
-        <v>0.2153658164044601</v>
+        <v>0.2170225122648286</v>
       </c>
       <c r="F7" s="2">
-        <v>1.707652359859478</v>
+        <v>1.730066787913986</v>
       </c>
       <c r="G7" s="2">
-        <v>88.68794867878418</v>
+        <v>88.69954608671731</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.5665765641941938</v>
+        <v>0.569752699833504</v>
       </c>
       <c r="C8" s="2">
-        <v>6.420182953833936</v>
+        <v>6.389478668642217</v>
       </c>
       <c r="D8" s="2">
-        <v>2.596172935660726</v>
+        <v>2.582980738387279</v>
       </c>
       <c r="E8" s="2">
-        <v>0.2183839587055787</v>
+        <v>0.2214856339835337</v>
       </c>
       <c r="F8" s="2">
-        <v>1.777614880652403</v>
+        <v>1.802434814486688</v>
       </c>
       <c r="G8" s="2">
-        <v>88.42106870695316</v>
+        <v>88.43386744466677</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.5574923594366716</v>
+        <v>0.5747126436781609</v>
       </c>
       <c r="C9" s="2">
-        <v>6.368927863867431</v>
+        <v>6.349499047267811</v>
       </c>
       <c r="D9" s="2">
-        <v>2.659991092408582</v>
+        <v>2.618476857827771</v>
       </c>
       <c r="E9" s="2">
-        <v>0.2365119100640425</v>
+        <v>0.2397197123363452</v>
       </c>
       <c r="F9" s="2">
-        <v>1.804555157956169</v>
+        <v>1.828631138975966</v>
       </c>
       <c r="G9" s="2">
-        <v>88.37252161626711</v>
+        <v>88.38896059991394</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.5532968544615291</v>
+        <v>0.5792715545569872</v>
       </c>
       <c r="C10" s="2">
-        <v>6.329288050622077</v>
+        <v>6.304736576642671</v>
       </c>
       <c r="D10" s="2">
-        <v>2.853605600220096</v>
+        <v>2.789368303605545</v>
       </c>
       <c r="E10" s="2">
-        <v>0.2567786506893284</v>
+        <v>0.2583031470188149</v>
       </c>
       <c r="F10" s="2">
-        <v>1.857059884449607</v>
+        <v>1.881486236569</v>
       </c>
       <c r="G10" s="2">
-        <v>88.14997095955736</v>
+        <v>88.18683418160698</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.5456753308637041</v>
+        <v>0.5760988124683145</v>
       </c>
       <c r="C11" s="2">
-        <v>6.300628679465698</v>
+        <v>6.257201235155854</v>
       </c>
       <c r="D11" s="2">
-        <v>2.920515855326867</v>
+        <v>2.846696265343431</v>
       </c>
       <c r="E11" s="2">
-        <v>0.2582350861552177</v>
+        <v>0.264237321985467</v>
       </c>
       <c r="F11" s="2">
-        <v>1.902946646786664</v>
+        <v>1.921865638394298</v>
       </c>
       <c r="G11" s="2">
-        <v>88.07199840140186</v>
+        <v>88.13390072665264</v>
       </c>
     </row>
     <row r="12" spans="1:7">
